--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,11 +521,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Miniature computer device connected to screens for content reproduction.</t>
+          <t>Hardware device (miniature computer) connected to screens for content reproduction.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0243</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.5508</v>
+        <v>0.5505</v>
       </c>
     </row>
     <row r="4">
@@ -615,28 +615,28 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>HTTP communication between presentation layer and API Gateway.</t>
+          <t>The API Gateway communicates with the Core service.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.2881</v>
+        <v>0.2497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -661,88 +661,88 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Backend framework used for developing microservices.</t>
+          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.07580000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>CF_M01_AU04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
+          <t>CF_M01_AU24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Core layer responsible for processing information and user requests.</t>
+          <t>Backend framework used for developing microservices.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>via the HTTP protocol</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -750,10 +750,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU25, CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>CF_M01_AU05, CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
@@ -771,59 +775,63 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M01_AU05, CF_M01_AU10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway service</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>Service responsible for management, authentication, authorization, and routing requests between clients and microservices.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.5903</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -834,15 +842,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>via the HTTP protocol</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU25, CF_M01_AU33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -869,103 +877,191 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AWS cloud services suite</t>
-        </is>
-      </c>
+          <t>CF_M01_AU28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>44</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Cloud Services</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Collection of AWS services forming a data lake for historical data processing.</t>
+          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.7198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M01_AU06, CF_M01_AU07</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cloud Services</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AWS cloud services suite</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>44, 45</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Cloud Services Set</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>Collection of AWS services forming a data lake for historical data processing.</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>0.2368</v>
+      <c r="L12" t="n">
+        <v>0.6069</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M01_AD03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Both the business layer and the data layer are divided into several different services</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CF_M01_AU06, CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>The Core service communicates with the Cloud Services Set.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.194</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,14 +504,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -521,11 +521,11 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Hardware device (miniature computer) connected to screens for content reproduction.</t>
+          <t>Hardware device (miniature computer) that connects screens to the platform to reproduce content.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0252</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="3">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.5505</v>
+        <v>0.5516</v>
       </c>
     </row>
     <row r="4">
@@ -615,7 +615,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.2497</v>
+        <v>0.2176</v>
       </c>
     </row>
     <row r="5">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.0755</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
+          <t>CF_M01_AU25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>more specifically with the Api Gateway</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -750,49 +750,49 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU06</t>
+          <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>presentation layer, business layer</t>
+          <t>presentation layer, api gateway service</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>Service responsible for management, authentication, and authorization of users, acting as the entry point for the business layer.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.5799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>more specifically with the Api Gateway</t>
+          <t>via the HTTP protocol</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -800,38 +800,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>presentation layer, api gateway service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU25, CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Service responsible for management, authentication, authorization, and routing requests between clients and microservices.</t>
+          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.5903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -842,15 +838,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>via the HTTP protocol</t>
+          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU25, CF_M01_AU33</t>
+          <t>CF_M01_AU26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -877,7 +873,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -896,7 +892,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -923,145 +919,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>CF_M01_AU11, CF_M01_AU15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>core service, sql database</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
+          <t>AU_39</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AWS cloud services suite</t>
+          <t>Service-oriented</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
+          <t>Both the business layer and the data layer are divided into several different services</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>42</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU06, CF_M01_AU07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Cloud Services Set</t>
-        </is>
-      </c>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Collection of AWS services forming a data lake for historical data processing.</t>
+          <t>The Core service communicates with the Cloud Services.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.6069</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M01_AD03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>42</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M01_AU06, CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>The Core service communicates with the Cloud Services Set.</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.194</v>
+        <v>0.2009</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU01</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The client is the user of the platform</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -511,42 +511,42 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Hardware device (miniature computer) that connects screens to the platform to reproduce content.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0234</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The server is the software that is responsible for processing user requests.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -554,44 +554,48 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>CF_M01_AU01, CF_M01_AU02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>customer, server</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>The platform is a web service where the client makes requests to a server that processes them and returns the response.</t>
+          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.5516</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,134 +608,134 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU01, CF_M01_AU02</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>customer, server</t>
-        </is>
-      </c>
+          <t>CF_M01_AU24</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The API Gateway communicates with the Core service.</t>
+          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.2176</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU03</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.7358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Waapiti Mobile Platform</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Backend framework used for developing microservices.</t>
+          <t>L’únic component que interactua de manera directa amb la capa de presentació és el mòdul Api Gateway.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.0762</v>
+        <v>0.6101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU25</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -742,7 +746,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>more specifically with the Api Gateway</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -750,87 +754,91 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU10</t>
+          <t>CF_M01_AU05, CF_M01_AU06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway service</t>
+          <t>presentation layer, business layer</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Service responsible for management, authentication, and authorization of users, acting as the entry point for the business layer.</t>
+          <t>Capa de presentació: És la capa que s’encarrega de mostrar la informació a l’usuari.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.5799</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU34</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>via the HTTP protocol</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU25, CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M01_AU27, CF_M01_AU14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells. Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.8249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>CF_M01_AU35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AWSS RDS</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -838,7 +846,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -846,166 +854,78 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
+          <t>CF_M01_AU15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>Aquesta base de dades està implementada en el servei RDS, que és un servei de base de dades relacional distribuït d’AWS.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>communication between the Api Gateway service is via the TCP communication protocol</t>
+          <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU06, CF_M01_AU07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Layer responsible for displaying information to the user, including web and mobile platforms.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU42</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The Analytical Module communicates with the Database.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU11, CF_M01_AU15</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>core service, sql database</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AU_39</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>The Analytical Module communicates with the Database.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M01_P03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>42</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M01_AU06, CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>The Core service communicates with the Cloud Services.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2009</v>
+        <v>0.703</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -565,21 +565,17 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
+          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7941</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="4">
@@ -625,7 +621,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
+          <t>Communication protocol used between the client and the server.</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -675,7 +671,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>La comunicació entre els dos components es realitza a través d’internet mitjançant el protocol HTTP.</t>
+          <t>Communication protocol used between the client and the server.</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -715,7 +711,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -725,7 +721,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L’únic component que interactua de manera directa amb la capa de presentació és el mòdul Api Gateway.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -765,7 +761,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -775,7 +771,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Capa de presentació: És la capa que s’encarrega de mostrar la informació a l’usuari.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -785,18 +781,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>CF_M01_AU32</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MySQL</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -804,28 +804,28 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU27, CF_M01_AU14</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
+          <t>CF_M01_AU15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells. Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.8249</v>
+        <v>0.7872</v>
       </c>
     </row>
     <row r="9">
@@ -866,16 +866,16 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Amazon RDS</t>
+          <t>AWS Cloud Services</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Aquesta base de dades està implementada en el servei RDS, que és un servei de base de dades relacional distribuït d’AWS.</t>
+          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.742</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,72 +481,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The server is the software that is responsible for processing user requests.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CF_M01_P01</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>User</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
+          <t>The client is the user of the platform.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8237</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -554,44 +550,44 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M01_AU01, CF_M01_AU02</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>customer, server</t>
-        </is>
-      </c>
+          <t>CF_M01_P01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.823</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,14 +600,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M01_AU01, CF_M01_AU02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>customer, server</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -621,72 +621,72 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Communication protocol used between the client and the server.</t>
+          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Web platform interface</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Communication protocol used between the client and the server.</t>
+          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7358</v>
+        <v>0.6775</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_AU08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>Web platform interface</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,38 +711,42 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
+          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6101</v>
+        <v>0.7358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>CF_M01_AU09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Waapiti Mobile Platform</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -750,103 +754,95 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
+          <t>CF_M01_AU05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.887</v>
+        <v>0.6101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M01_AU32</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MySQL</t>
-        </is>
-      </c>
+          <t>CF_M01_AU30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M01_AU05, CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7872</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M01_AU35</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AWSS RDS</t>
-        </is>
-      </c>
+          <t>CF_M01_AU28</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>This service is responsible for communicating with players.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -854,77 +850,123 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>CF_M01_AU27, CF_M01_AU13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AWS Cloud Services</t>
-        </is>
-      </c>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.658</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M01_AU06, CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>CF_M01_AU27, CF_M01_AU14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8186</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Both the business layer and the data layer are divided into several different services</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>42</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_M01_AU06, CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>0.703</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,47 +481,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU27</t>
+          <t>CF_M01_AU01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>The client is the user of the platform</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CF_M01_P01</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The client is the user of the platform.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7565</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="3">
@@ -605,148 +609,140 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>customer, server</t>
+          <t>client, server</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
+          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7941</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
+          <t>CF_M01_AU30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M01_AU05, CF_M01_AU06</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>presentation layer, business layer</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>This database is implemented in the RDS service, which is a distributed relational database service from AWS.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6775</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU08</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Web platform interface</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>CF_M01_AU27, CF_M01_AU14</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
+          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them. [...] It processes the data coming from the players and stores them in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.7358</v>
+        <v>0.8564000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_AU09</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Waapiti Mobile Platform</t>
+          <t>Service-oriented</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
+          <t>Both the business layer and the data layer are divided into several different services</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -754,220 +750,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU05</t>
+          <t>CF_M01_AU06, CF_M01_AU07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Database Service</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users.</t>
+          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.6101</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M01_AU30</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>the presentation layer communicates with the business layer</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>42</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M01_AU05, CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AU_02</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Presentation Layer</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.887</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M01_AU28</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>This service is responsible for communicating with players.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>44</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M01_AU27, CF_M01_AU13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>player, api player</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7808</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>44</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M01_AU27, CF_M01_AU14</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>player, web socket</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.8186</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M01_P03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>42</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU06, CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.703</v>
+        <v>0.7045</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -615,73 +615,73 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, using the HTTP protocol.</t>
+          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, through the HTTP protocol.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.823</v>
+        <v>0.8183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>CF_M01_AU04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU05, CF_M01_AU06</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>presentation layer, business layer</t>
-        </is>
-      </c>
+          <t>CF_M01_AU24</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>The communication between the two components is carried out through the internet using the HTTP protocol.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.887</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -692,36 +692,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_AU27, CF_M01_AU14</t>
+          <t>CF_M01_AU05, CF_M01_AU06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>player, web socket</t>
+          <t>presentation layer, business layer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them. [...] It processes the data coming from the players and stores them in the database and in the cloud services.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="7">
@@ -757,21 +761,21 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Database Service</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7045</v>
+        <v>0.703</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>GT_fixes</t>
+          <t>GT_fixedType</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -481,62 +481,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_AU01</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The client is the user of the platform</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CF_M01_P01</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>User</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
+          <t>The client is the user of the platform.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8333</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_AU02</t>
+          <t>CF_M01_AU01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -546,7 +542,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The server is the software that is responsible for processing user requests.</t>
+          <t>The client is the user of the platform</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -575,28 +571,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.8237</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>The server is the software that is responsible for processing user requests.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -604,44 +600,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_AU01, CF_M01_AU02</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>client, server</t>
-        </is>
-      </c>
+          <t>CF_M01_P01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The presentation layer communicates with the business layer, more specifically with the Api Gateway, through the HTTP protocol.</t>
+          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8183</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
+          <t>CF_M01_AU24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -654,14 +646,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M01_AU01, CF_M01_AU02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>client, server</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -675,7 +671,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="6">
@@ -731,51 +727,193 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M01_P03</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Service-oriented</t>
-        </is>
-      </c>
+          <t>CF_M01_AU28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Both the business layer and the data layer are divided into several different services</t>
+          <t>This service is responsible for communicating with players.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M01_AU06, CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>CF_M01_AU27, CF_M01_AU13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>player, api player</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>En el nostre projecte la plataforma de Waapiti és un servei web que segueix l’arquitectura client-servidor.</t>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.703</v>
+        <v>0.8078</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>This service is responsible for communicating between the platform and the players.</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M01_AU27, CF_M01_AU14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>player, web socket</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells.</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.847</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M01_AU35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AWSS RDS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M01_AU15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>This database is implemented in the RDS service.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.742</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M01_P03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Service-oriented</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Both the business layer and the data layer are divided into several different services</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>42</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M01_AU06, CF_M01_AU07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Core Service</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>This service is responsible for performing the business logic of the platform, it would be the main core of the platform.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.766</v>
       </c>
     </row>
   </sheetData>
